--- a/415-rc---harmonisation-des-value-sets-et-code-systems/ig/StructureDefinition-tddui-event-label.xlsx
+++ b/415-rc---harmonisation-des-value-sets-et-code-systems/ig/StructureDefinition-tddui-event-label.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-28T14:23:39+00:00</t>
+    <t>2026-01-28T15:00:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/415-rc---harmonisation-des-value-sets-et-code-systems/ig/StructureDefinition-tddui-event-label.xlsx
+++ b/415-rc---harmonisation-des-value-sets-et-code-systems/ig/StructureDefinition-tddui-event-label.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-28T15:00:38+00:00</t>
+    <t>2026-01-28T15:51:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/415-rc---harmonisation-des-value-sets-et-code-systems/ig/StructureDefinition-tddui-event-label.xlsx
+++ b/415-rc---harmonisation-des-value-sets-et-code-systems/ig/StructureDefinition-tddui-event-label.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-28T15:51:30+00:00</t>
+    <t>2026-02-02T09:49:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/415-rc---harmonisation-des-value-sets-et-code-systems/ig/StructureDefinition-tddui-event-label.xlsx
+++ b/415-rc---harmonisation-des-value-sets-et-code-systems/ig/StructureDefinition-tddui-event-label.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-02T09:49:54+00:00</t>
+    <t>2026-02-02T14:44:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/415-rc---harmonisation-des-value-sets-et-code-systems/ig/StructureDefinition-tddui-event-label.xlsx
+++ b/415-rc---harmonisation-des-value-sets-et-code-systems/ig/StructureDefinition-tddui-event-label.xlsx
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Libellé de l'évènement</t>
+    <t>TDDUI Event Label</t>
   </si>
   <si>
     <t>Status</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-02T14:44:55+00:00</t>
+    <t>2026-02-04T16:15:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/415-rc---harmonisation-des-value-sets-et-code-systems/ig/StructureDefinition-tddui-event-label.xlsx
+++ b/415-rc---harmonisation-des-value-sets-et-code-systems/ig/StructureDefinition-tddui-event-label.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-04T16:15:13+00:00</t>
+    <t>2026-02-05T08:25:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
